--- a/CodeSystem-CS-BetelNutObservable.xlsx
+++ b/CodeSystem-CS-BetelNutObservable.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -144,7 +144,7 @@
     <t>嚼檳榔狀態</t>
   </si>
   <si>
-    <t>受檢者目前之嚼檳榔狀態。本碼為**問題**（Observation.code），答案以 `value[x]` 承載，值集為 VS-BetelNutStatus（從未／偶爾／每日／已戒除，四級序位）。⚠️ 本碼**不表示受檢者有嚼檳榔**——它問的是狀態，答案可以是「從未嚼食檳榔」。此與 SNOMED CT `698188003`（Chews betel quid）之語意不同：後者是肯定式 finding，斷言此人嚼檳，故不得置於 `.code`。角色對應吸菸之 `LNC#72166-2`（Tobacco smoking status）。</t>
+    <t>受檢者目前之嚼檳榔狀態。本碼是問題，用於 Observation.code；答案以 value[x] 承載，值集為 VS-BetelNutStatus（從未／偶爾／每日／已戒除，四級序位）。⚠️ 本碼並不表示受檢者有嚼檳榔——它問的是狀態，答案可以是「從未嚼食檳榔」。此與 SNOMED CT 698188003（Chews betel quid）之語意不同：後者是肯定式 finding，斷言此人嚼檳，故不得置於 Observation.code。角色對應吸菸之 LOINC 72166-2（Tobacco smoking status）。</t>
   </si>
 </sst>
 </file>

--- a/CodeSystem-CS-BetelNutObservable.xlsx
+++ b/CodeSystem-CS-BetelNutObservable.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutObservable.xlsx
+++ b/CodeSystem-CS-BetelNutObservable.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutObservable.xlsx
+++ b/CodeSystem-CS-BetelNutObservable.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutObservable.xlsx
+++ b/CodeSystem-CS-BetelNutObservable.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutObservable.xlsx
+++ b/CodeSystem-CS-BetelNutObservable.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutObservable.xlsx
+++ b/CodeSystem-CS-BetelNutObservable.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
